--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nazil\1 A CHARUSAT\1 Visual Studio Code\Personal\DOA\1_Excel_DOA_Course\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8063926F-B2A1-472D-9C76-ECB79527680F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06354CF7-9577-496A-9D29-1A421BCFC82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>

--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nazil\1 A CHARUSAT\1 Visual Studio Code\Personal\DOA\1_Excel_DOA_Course\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1 Visual Studio Code\Personal\DOA\1_Excel_DOA_Course\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06354CF7-9577-496A-9D29-1A421BCFC82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393F6D00-3C1E-4CAB-95D7-262FBD817387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>
@@ -578,7 +578,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -935,12 +935,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1036,6 +1045,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4217,7 +4229,7 @@
     <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -4272,12 +4284,14 @@
       <c r="R1" s="35" t="s">
         <v>143</v>
       </c>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
       <c r="XFD1">
         <f>SUM(Q1:XFC1)</f>
         <v>85000</v>
       </c>
     </row>
-    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
@@ -4341,7 +4355,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -4405,7 +4419,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
@@ -4467,7 +4481,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
@@ -4529,7 +4543,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
@@ -4591,7 +4605,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -4653,7 +4667,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
@@ -4715,7 +4729,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -4779,7 +4793,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
@@ -4841,7 +4855,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
@@ -4905,7 +4919,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
@@ -4969,7 +4983,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
@@ -5033,7 +5047,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
@@ -5097,7 +5111,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
@@ -5161,7 +5175,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21 16384:16384" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
